--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Иполитов- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Иполитов- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9257366896</v>
+        <v>46157.93114751789</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Иполитов- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Иполитов- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93114751789</v>
+        <v>46157.93181473742</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Иполитов- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Иполитов- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93181473742</v>
+        <v>46157.93405019236</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Иполитов- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Иполитов- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93405019236</v>
+        <v>46157.93723092815</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Иполитов- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Иполитов- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93723092815</v>
+        <v>46158.28220938035</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Иполитов- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Иполитов- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28220938035</v>
+        <v>46158.29698350434</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Иполитов- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Иполитов- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29698350434</v>
+        <v>46158.29820596965</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Иполитов- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Иполитов- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29820596965</v>
+        <v>46158.33391935568</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Иполитов- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Иполитов- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33391935568</v>
+        <v>46158.36861739575</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Иполитов- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Иполитов- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36861739575</v>
+        <v>46158.37292375768</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
